--- a/data/out/best_models_lstm/in/best_models_lstm.xlsx
+++ b/data/out/best_models_lstm/in/best_models_lstm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\out\best_models_lstm\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC3CCB5-7E2F-4264-A48D-99D736A707BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469048CE-F3FD-4161-86C4-A1837731AA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,15 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
   <si>
     <t>variant</t>
   </si>
   <si>
     <t>model</t>
-  </si>
-  <si>
-    <t>config</t>
   </si>
   <si>
     <t>R2</t>
@@ -462,59 +459,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
       </c>
       <c r="D2">
         <v>0.60364526510238647</v>
@@ -532,7 +526,7 @@
         <v>123.1028199195862</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2">
         <v>48168</v>
@@ -547,15 +541,15 @@
         <v>80.602914810180664</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>0.87740212678909302</v>
@@ -573,7 +567,7 @@
         <v>165.5485272407532</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3">
         <v>48144</v>
@@ -588,15 +582,15 @@
         <v>144.98711585998541</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>0.4091949462890625</v>
@@ -614,7 +608,7 @@
         <v>98.911064863204956</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4">
         <v>48168</v>
@@ -628,19 +622,16 @@
       <c r="M4">
         <v>132.97264671325681</v>
       </c>
-      <c r="Q4">
-        <v>347.02</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>0.87036663293838501</v>
@@ -658,7 +649,7 @@
         <v>164.80123996734619</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5">
         <v>48144</v>
@@ -673,15 +664,15 @@
         <v>139.01584815979001</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>0.25670230388641357</v>
@@ -699,7 +690,7 @@
         <v>85.815006494522095</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6">
         <v>48168</v>
@@ -714,15 +705,15 @@
         <v>134.53748226165769</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>0.87362682819366455</v>
@@ -740,7 +731,7 @@
         <v>163.37939500808719</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7">
         <v>48144</v>
@@ -755,15 +746,15 @@
         <v>153.63896870613101</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D8">
         <v>0.50324338674545288</v>
@@ -781,7 +772,7 @@
         <v>116.370701789856</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8">
         <v>48168</v>
@@ -796,15 +787,15 @@
         <v>141.92224812507629</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>0.86347675323486328</v>
@@ -822,7 +813,7 @@
         <v>154.86718416213989</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9">
         <v>48144</v>
@@ -837,15 +828,15 @@
         <v>150.65522623062131</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>0.44698035717010498</v>
@@ -863,7 +854,7 @@
         <v>110.8086824417114</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10">
         <v>48168</v>
@@ -878,15 +869,15 @@
         <v>126.779096364975</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>0.86752408742904663</v>
@@ -904,7 +895,7 @@
         <v>157.55463838577271</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11">
         <v>48144</v>
@@ -919,15 +910,15 @@
         <v>170.65830969810489</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>0.34155994653701782</v>
@@ -945,7 +936,7 @@
         <v>102.8270959854126</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12">
         <v>48168</v>
@@ -960,15 +951,15 @@
         <v>125.72546052932741</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>0.87478697299957275</v>
@@ -986,7 +977,7 @@
         <v>169.64360475540161</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13">
         <v>48144</v>
@@ -1001,15 +992,15 @@
         <v>140.1363391876221</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>28</v>
       </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>0.45043390989303589</v>
@@ -1027,7 +1018,7 @@
         <v>131.84355497360229</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14">
         <v>48168</v>
@@ -1042,15 +1033,15 @@
         <v>374.51655411720282</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>0.51323062181472778</v>
@@ -1068,7 +1059,7 @@
         <v>130.85980415344241</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15">
         <v>48168</v>
@@ -1083,12 +1074,12 @@
         <v>1354.973567247391</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -1109,7 +1100,7 @@
         <v>134.47889089584351</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16">
         <v>48168</v>
@@ -1126,13 +1117,13 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>0.4579741358757019</v>
@@ -1150,7 +1141,7 @@
         <v>120.8537340164185</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J17">
         <v>48168</v>
@@ -1167,13 +1158,13 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>-0.7</v>
@@ -1191,7 +1182,7 @@
         <v>96.7</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18">
         <v>13081</v>
@@ -1208,13 +1199,13 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>0.33</v>
@@ -1232,7 +1223,7 @@
         <v>46.33</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19">
         <v>13057</v>
@@ -1249,13 +1240,13 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
         <v>37</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>-0.64</v>
@@ -1273,7 +1264,7 @@
         <v>86.95</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20">
         <v>13081</v>
@@ -1290,13 +1281,13 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D21">
         <v>0.32</v>
@@ -1314,7 +1305,7 @@
         <v>43.46</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21">
         <v>13057</v>

--- a/data/out/best_models_lstm/in/best_models_lstm.xlsx
+++ b/data/out/best_models_lstm/in/best_models_lstm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\out\best_models_lstm\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469048CE-F3FD-4161-86C4-A1837731AA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A6560C-1FD8-40C5-87D6-9575ECC51EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
   <si>
     <t>variant</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>v10_date_range_no_solar_lags</t>
+  </si>
+  <si>
+    <t>config</t>
   </si>
 </sst>
 </file>
@@ -469,6 +472,9 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
